--- a/artfynd/A 30655-2024 artfynd.xlsx
+++ b/artfynd/A 30655-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1323,6 +1323,249 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118886978</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8405</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Piltorp (Piltorp), Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>585718</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6577489</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118887482</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Backa (Backa), Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>585816</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6577337</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30655-2024 artfynd.xlsx
+++ b/artfynd/A 30655-2024 artfynd.xlsx
@@ -1325,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118886978</v>
+        <v>118887482</v>
       </c>
       <c r="B7" t="n">
-        <v>8405</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,38 +1337,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Piltorp (Piltorp), Srm</t>
+          <t>Backa (Backa), Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585718</v>
+        <v>585816</v>
       </c>
       <c r="R7" t="n">
-        <v>6577489</v>
+        <v>6577337</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1400,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1410,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1433,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog på blockmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,10 +1451,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118887482</v>
+        <v>118886978</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>8405</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1454,47 +1463,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backa (Backa), Srm</t>
+          <t>Piltorp (Piltorp), Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585816</v>
+        <v>585718</v>
       </c>
       <c r="R8" t="n">
-        <v>6577337</v>
+        <v>6577489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 30655-2024 artfynd.xlsx
+++ b/artfynd/A 30655-2024 artfynd.xlsx
@@ -1325,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118887482</v>
+        <v>118886978</v>
       </c>
       <c r="B7" t="n">
-        <v>97853</v>
+        <v>8405</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,47 +1337,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Backa (Backa), Srm</t>
+          <t>Piltorp (Piltorp), Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585816</v>
+        <v>585718</v>
       </c>
       <c r="R7" t="n">
-        <v>6577337</v>
+        <v>6577489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,7 +1424,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1451,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118886978</v>
+        <v>118887482</v>
       </c>
       <c r="B8" t="n">
-        <v>8405</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,38 +1454,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Piltorp (Piltorp), Srm</t>
+          <t>Backa (Backa), Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585718</v>
+        <v>585816</v>
       </c>
       <c r="R8" t="n">
-        <v>6577489</v>
+        <v>6577337</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Barrskog på blockmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
